--- a/WorkBot/refactor-experimental/data/orders/Coffee Depot LLC/Coffee Depot LLC_Syracuse_20251114.xlsx
+++ b/WorkBot/refactor-experimental/data/orders/Coffee Depot LLC/Coffee Depot LLC_Syracuse_20251114.xlsx
@@ -450,20 +450,14 @@
           <t>Monin - Vanilla Sugar Free</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>9.00</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>36.00</t>
-        </is>
+      <c r="C2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D2" t="n">
+        <v>9</v>
+      </c>
+      <c r="E2" t="n">
+        <v>36</v>
       </c>
     </row>
     <row r="3">
@@ -473,20 +467,14 @@
           <t>Monin - Peppermint</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>9.00</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>18.00</t>
-        </is>
+      <c r="C3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" t="n">
+        <v>9</v>
+      </c>
+      <c r="E3" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="4">
@@ -496,20 +484,14 @@
           <t>Monin - Hazelnut</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>9.00</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>18.00</t>
-        </is>
+      <c r="C4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" t="n">
+        <v>9</v>
+      </c>
+      <c r="E4" t="n">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
